--- a/apps/web/public/importmallar/importmall-kundadresser.xlsx
+++ b/apps/web/public/importmallar/importmall-kundadresser.xlsx
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -158,6 +158,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,12 +170,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1" style="4"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1" style="4"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
@@ -254,88 +255,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kundnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numret på en kund som redan finns i kundregistret — importera kunderna först.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressnamn</t>
+          <t xml:space="preserve">Kundnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveransadressens benämning på kundkortet, max 100 tecken. Tom cell ger Leveransadress.</t>
+          <t xml:space="preserve">Numret på en kund som redan finns i kundregistret — importera kunderna först.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelskolan, köket</t>
+          <t xml:space="preserve">1001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 1</t>
+          <t xml:space="preserve">Adressnamn</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -345,19 +331,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Första adressraden. Raderna 1–3 slås ihop till en adress med radbrytningar. En rad utan någon adressrad hoppas över, liksom en adress som är samma som kundens besöksadress eller en leveransadress som redan finns. Den första nya adressen blir kundens förvalda om kunden saknar en och guidens Sätt som förvald leveransadress är ikryssad.</t>
+          <t xml:space="preserve">Leveransadressens benämning på kundkortet, max 100 tecken. Tom cell ger Leveransadress.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolvägen 5</t>
+          <t xml:space="preserve">Exempelskolan, köket</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 2</t>
+          <t xml:space="preserve">Adressrad 1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -367,19 +353,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andra adressraden, valfri — slås ihop med Adressrad 1.</t>
+          <t xml:space="preserve">Första adressraden. Raderna 1–3 slås ihop till en adress med radbrytningar. En rad utan någon adressrad hoppas över, liksom en adress som är samma som kundens besöksadress eller en leveransadress som redan finns. Den första nya adressen blir kundens förvalda om kunden saknar en och guidens Sätt som förvald leveransadress är ikryssad.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varumottagningen</t>
+          <t xml:space="preserve">Skolvägen 5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 3</t>
+          <t xml:space="preserve">Adressrad 2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -389,19 +375,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tredje adressraden, valfri — slås ihop med Adressrad 1.</t>
+          <t xml:space="preserve">Andra adressraden, valfri — slås ihop med Adressrad 1.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Port 3</t>
+          <t xml:space="preserve">Varumottagningen</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postnummer</t>
+          <t xml:space="preserve">Adressrad 3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -411,19 +397,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 20 tecken.</t>
+          <t xml:space="preserve">Tredje adressraden, valfri — slås ihop med Adressrad 1.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123 42</t>
+          <t xml:space="preserve">Port 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stad</t>
+          <t xml:space="preserve">Postnummer</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -433,32 +419,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 100 tecken.</t>
+          <t xml:space="preserve">Max 20 tecken.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelby</t>
+          <t xml:space="preserve">123 42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stad</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max 100 tecken.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exempelby</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Land</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Landskod med två bokstäver (t.ex. SE); små bokstäver godtas. Tom cell ger SE.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SE</t>
         </is>

--- a/apps/web/public/importmallar/importmall-kundadresser.xlsx
+++ b/apps/web/public/importmallar/importmall-kundadresser.xlsx
@@ -107,6 +107,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Landskod med två bokstäver (t.ex. SE); små bokstäver godtas. Tom cell ger SE.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja gör adressen till kundens förvalda leveransadress. Är kolumnen med avgör den per rad i stället för kryssrutan Sätt som förvald leveransadress; har kunden redan en förvald adress blir det en varning och adressen läggs till utan att vara förvald.</t>
         </r>
       </text>
     </comment>
@@ -178,6 +190,7 @@
     <col min="6" max="6" width="14" customWidth="1" style="4"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -219,6 +232,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Land</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Förvald</t>
         </is>
       </c>
     </row>
@@ -472,6 +490,28 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Förvald</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja gör adressen till kundens förvalda leveransadress. Är kolumnen med avgör den per rad i stället för kryssrutan Sätt som förvald leveransadress; har kunden redan en förvald adress blir det en varning och adressen läggs till utan att vara förvald.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
